--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20212.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20212.xlsx
@@ -474,19 +474,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -500,19 +500,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -526,19 +526,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -591,16 +591,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +617,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -637,16 +643,19 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -699,19 +708,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,19 +734,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -751,19 +760,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20212.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20212.xlsx
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
